--- a/data/B24_department_schedules_midterms/Jeoloji Mühendisliği.xlsx
+++ b/data/B24_department_schedules_midterms/Jeoloji Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_midterms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD95B7B-5681-492C-B295-E41BB8D30AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{ACD95B7B-5681-492C-B295-E41BB8D30AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4140CA2D-2271-4F62-9072-59405FFE19F1}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
   <si>
     <t>Year:</t>
   </si>
@@ -194,6 +194,9 @@
   </si>
   <si>
     <t>YLAB 2</t>
+  </si>
+  <si>
+    <t>timeslots</t>
   </si>
 </sst>
 </file>
@@ -274,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -291,11 +294,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -373,16 +383,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{504945AA-73F9-49EF-A751-53C7164FA7B0}" name="Table1" displayName="Table1" ref="A1:F24" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A1:F24" xr:uid="{504945AA-73F9-49EF-A751-53C7164FA7B0}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6CDCABA3-28D2-4C26-8D49-8A832BC0257F}" name="Year:" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{6C2A0639-5A0E-4ADF-96FC-977DF86DFA34}" name="Course ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{EAFB78A6-4040-46CC-BFDE-326E33A1F28A}" name="Date" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{A1385BCE-6BD2-469A-A025-5D100CB06910}" name="Rooms" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{48C9C8DE-3CCF-4788-983A-2D34BE14D436}" name="Course Name" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{FD100ABD-2F3E-43DD-8DC3-8F9166DEA175}" name="Rooms Used" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{504945AA-73F9-49EF-A751-53C7164FA7B0}" name="Table1" displayName="Table1" ref="A1:G24" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G24" xr:uid="{504945AA-73F9-49EF-A751-53C7164FA7B0}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{6CDCABA3-28D2-4C26-8D49-8A832BC0257F}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{6C2A0639-5A0E-4ADF-96FC-977DF86DFA34}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{EAFB78A6-4040-46CC-BFDE-326E33A1F28A}" name="Date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{A1385BCE-6BD2-469A-A025-5D100CB06910}" name="Rooms" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{48C9C8DE-3CCF-4788-983A-2D34BE14D436}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{FD100ABD-2F3E-43DD-8DC3-8F9166DEA175}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{2A7592C2-7D2A-4BFE-A647-244AE09F2360}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -675,15 +690,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="37.26953125" customWidth="1"/>
-    <col min="6" max="6" width="44.90625" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="37.265625" customWidth="1"/>
+    <col min="6" max="6" width="44.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -702,8 +717,11 @@
       <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -722,8 +740,12 @@
       <c r="F2" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" s="7">
+        <v>5</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -742,8 +764,12 @@
       <c r="F3" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="7">
+        <v>5</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -762,8 +788,12 @@
       <c r="F4" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" s="7">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -782,8 +812,12 @@
       <c r="F5" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="7">
+        <v>5</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -802,8 +836,11 @@
       <c r="F6" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -822,8 +859,12 @@
       <c r="F7" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -842,8 +883,12 @@
       <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -862,8 +907,12 @@
       <c r="F9" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" s="7">
+        <v>5</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -882,8 +931,12 @@
       <c r="F10" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -902,8 +955,11 @@
       <c r="F11" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -922,8 +978,11 @@
       <c r="F12" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -942,8 +1001,11 @@
       <c r="F13" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>3</v>
       </c>
@@ -962,8 +1024,11 @@
       <c r="F14" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -982,8 +1047,11 @@
       <c r="F15" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -1002,8 +1070,11 @@
       <c r="F16" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>3</v>
       </c>
@@ -1022,8 +1093,11 @@
       <c r="F17" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1042,8 +1116,11 @@
       <c r="F18" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1062,8 +1139,11 @@
       <c r="F19" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="5">
         <v>4</v>
       </c>
@@ -1082,8 +1162,11 @@
       <c r="F20" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="5">
         <v>4</v>
       </c>
@@ -1102,8 +1185,11 @@
       <c r="F21" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="5">
         <v>4</v>
       </c>
@@ -1122,8 +1208,11 @@
       <c r="F22" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>4</v>
       </c>
@@ -1142,8 +1231,11 @@
       <c r="F23" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1161,6 +1253,9 @@
       </c>
       <c r="F24" s="5" t="s">
         <v>52</v>
+      </c>
+      <c r="G24" s="7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
